--- a/notes/Cumulative Vocabulary Table.xlsx
+++ b/notes/Cumulative Vocabulary Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Lessons ✒📝\Master\Term 3\Master's Theses\Paper\Paper_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681D223A-2CEF-4D26-B9D4-91C3118113B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F9F34F-DBD7-4D8A-9A1C-F5C58B91ED6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="390" windowWidth="17475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="735" windowWidth="17475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="372">
   <si>
     <t>کلمه تخصصی (English)</t>
   </si>
@@ -961,6 +961,189 @@
   </si>
   <si>
     <t>قابلیت بازگرداندن شبکه به حالت عادی پس از وقوع خطا (مثل قطعی لینک) [۳۹، ۴۰].</t>
+  </si>
+  <si>
+    <t>GraphSAGE</t>
+  </si>
+  <si>
+    <t>Transductive</t>
+  </si>
+  <si>
+    <t>انتقالی / ترانزداکتیو</t>
+  </si>
+  <si>
+    <t>مدلی که فقط روی گره‌های موجود در زمان آموزش کار می‌کند [۱، ۹].</t>
+  </si>
+  <si>
+    <t>Inductive</t>
+  </si>
+  <si>
+    <t>استقرایی</t>
+  </si>
+  <si>
+    <t>قابلیتی که اجازه می‌دهد مدل بدون آموزش مجدد، برای گره‌های کاملاً جدید خروجی تولید کند [۱، ۳].</t>
+  </si>
+  <si>
+    <t>Evolving Graphs</t>
+  </si>
+  <si>
+    <t>گراف‌های در حال تکامل</t>
+  </si>
+  <si>
+    <t>گراف‌هایی که ساختار (یال و گره) آن‌ها در طول زمان تغییر می‌کند (مانند شبکه موبایل) [۳، ۲۸].</t>
+  </si>
+  <si>
+    <t>Leverages</t>
+  </si>
+  <si>
+    <t>بهره‌برداری / به کار بستن</t>
+  </si>
+  <si>
+    <t>استفاده از ویژگی‌های موجود (مانند خروجی گوموری-هو) برای غنی‌سازی یادگیری [۱، ۶].</t>
+  </si>
+  <si>
+    <t>Node Embeddings</t>
+  </si>
+  <si>
+    <t>جای‌گذاری‌های گره</t>
+  </si>
+  <si>
+    <t>تبدیل ویژگی‌های پیچیده سایت رادیویی به یک بردار عددی فشرده برای عامل DRL [۱، ۲].</t>
+  </si>
+  <si>
+    <t>High-throughput</t>
+  </si>
+  <si>
+    <t>توان عملیاتی بالا</t>
+  </si>
+  <si>
+    <t>سیستم‌هایی که قادر به پردازش حجم عظیمی از داده در زمان بسیار کوتاه هستند [۳، ۹۰].</t>
+  </si>
+  <si>
+    <t>Aggregating</t>
+  </si>
+  <si>
+    <t>تجمیع / گردآوری</t>
+  </si>
+  <si>
+    <t>فرآیند ترکیب اطلاعات همسایگان برای درک وضعیت کلی یک منطقه از شبکه [۱، ۷].</t>
+  </si>
+  <si>
+    <t>Search Depth / Hops</t>
+  </si>
+  <si>
+    <t>عمق جستجو / گام‌ها</t>
+  </si>
+  <si>
+    <t>تعداد مراحلی که مدل در گراف پیش می‌رود تا اطلاعات همسایگان دورتر را جذب کند [13، 15].</t>
+  </si>
+  <si>
+    <t>Incrementally</t>
+  </si>
+  <si>
+    <t>گام‌به‌گام / افزایشی</t>
+  </si>
+  <si>
+    <t>فرآیند مرحله‌ایِ کسب اطلاعات وسیع‌تر از ساختار گراف در هر تکرار.</t>
+  </si>
+  <si>
+    <t>Fixed-size Sampling</t>
+  </si>
+  <si>
+    <t>نمونه‌برداری با اندازه ثابت</t>
+  </si>
+  <si>
+    <t>انتخاب تعداد محدودی همسایه (Sk​) برای جلوگیری از انفجار محاسباتی در گراف‌های متراکم.</t>
+  </si>
+  <si>
+    <t>Computational Footprint</t>
+  </si>
+  <si>
+    <t>ردپای محاسباتی</t>
+  </si>
+  <si>
+    <t>میزان منابع پردازشی و حافظه مورد نیاز که در GraphSAGE با نمونه‌برداری ثابت می‌شود.</t>
+  </si>
+  <si>
+    <t>Pooling Aggregator</t>
+  </si>
+  <si>
+    <t>تجمیع‌کننده حوضچه‌ای</t>
+  </si>
+  <si>
+    <t>نوعی تابع تجمیع که ویژگی‌ها را از طریق عملیاتی مانند بیشینه‌گیری ترکیب می‌کند [۲۳].</t>
+  </si>
+  <si>
+    <t>Fully-connected Neural Network</t>
+  </si>
+  <si>
+    <t>شبکه عصبی کاملاً متصل</t>
+  </si>
+  <si>
+    <t>لایه‌ای که تمام نورون‌های ورودی را به خروجی وصل کرده و در اینجا ویژگی‌های خام همسایه را متحول می‌کند [۲۳].</t>
+  </si>
+  <si>
+    <t>Elementwise Max-pooling</t>
+  </si>
+  <si>
+    <t>بیشینه‌گیری مؤلفه‌ای</t>
+  </si>
+  <si>
+    <t>انتخاب بزرگترین مقدار در هر درایه بردار از میان تمام بردارهای همسایه [۲۳].</t>
+  </si>
+  <si>
+    <t>Permutation Invariant</t>
+  </si>
+  <si>
+    <t>ناوردا نسبت به جایگشت</t>
+  </si>
+  <si>
+    <t>ویژگی مهمی که باعث می‌شود خروجی تابع تجمیع به ترتیب وارد شدن گره‌های همسایه وابسته نباشد [۲۰].</t>
+  </si>
+  <si>
+    <t>Unsupervised Loss</t>
+  </si>
+  <si>
+    <t>تابع زیان بدون نظارت</t>
+  </si>
+  <si>
+    <t>معیاری برای آموزش مدل بدون نیاز به برچسب‌های از پیش تعیین شده (Labels) [۱۸].</t>
+  </si>
+  <si>
+    <t>Random Walk</t>
+  </si>
+  <si>
+    <t>گشت تصادفی</t>
+  </si>
+  <si>
+    <t>فرآیندی که در آن مسیری در گراف با انتخاب تصادفی گره‌های همسایه پیموده می‌شود تا قرابت گره‌ها مشخص گردد [۱۹].</t>
+  </si>
+  <si>
+    <t>Negative Sampling</t>
+  </si>
+  <si>
+    <t>نمونه‌برداری منفی</t>
+  </si>
+  <si>
+    <t>تکنیکی برای افزایش کارایی آموزش با مقایسه گره هدف با گره‌هایی که در همسایگی آن نیستند [۱۹، ۵۸].</t>
+  </si>
+  <si>
+    <t>Disparate Nodes</t>
+  </si>
+  <si>
+    <t>گره‌های متمایز / دور</t>
+  </si>
+  <si>
+    <t>گره‌هایی که در ساختار گراف ارتباط نزدیکی با هم ندارند و باید امبدینگ‌های متفاوتی بگیرند [۱۸].</t>
+  </si>
+  <si>
+    <t>Sigmoid Function (σ)</t>
+  </si>
+  <si>
+    <t>تابع سیگموئید</t>
+  </si>
+  <si>
+    <t>تابعی که خروجی را به بازه (۰,۱) می‌برد تا به عنوان احتمال شباهت تفسیر شود [۱۹].</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr defaultColWidth="32.42578125" defaultRowHeight="22.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" style="9" bestFit="1" customWidth="1"/>
@@ -2723,6 +2906,231 @@
       </c>
       <c r="C120" s="13" t="s">
         <v>310</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A124" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A125" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C125" s="13" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A126" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A127" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A128" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A129" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A130" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A132" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="B132" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A133" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C133" s="13" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A134" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C134" s="13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A135" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="C135" s="13" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A136" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="C136" s="13" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A137" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C137" s="13" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A138" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C138" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A139" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B139" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C139" s="13" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A140" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C140" s="13" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A141" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C141" s="13" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A142" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="C142" s="13" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/notes/Cumulative Vocabulary Table.xlsx
+++ b/notes/Cumulative Vocabulary Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Lessons ✒📝\Master\Term 3\Master's Theses\Paper\Paper_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F9F34F-DBD7-4D8A-9A1C-F5C58B91ED6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B5218A-E8C2-4153-896C-22D3DD2A9E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="735" windowWidth="17475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="750" yWindow="1080" windowWidth="17475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="427">
   <si>
     <t>کلمه تخصصی (English)</t>
   </si>
@@ -1144,6 +1144,171 @@
   </si>
   <si>
     <t>تابعی که خروجی را به بازه (۰,۱) می‌برد تا به عنوان احتمال شباهت تفسیر شود [۱۹].</t>
+  </si>
+  <si>
+    <t>PPO</t>
+  </si>
+  <si>
+    <t>Probability Ratio (rt​)</t>
+  </si>
+  <si>
+    <t>نسبت احتمال</t>
+  </si>
+  <si>
+    <t>نسبت احتمال انتخاب یک عمل در سیاست جدید به سیاست قدیمی [۹۴].</t>
+  </si>
+  <si>
+    <t>Clipped Surrogate</t>
+  </si>
+  <si>
+    <t>جایگزین مقید شده</t>
+  </si>
+  <si>
+    <t>تابع هدفی که با بریدن (Clip) مقادیر بزرگ، از تغییرات افراطی سیاست جلوگیری می‌کند [۸۸، ۹۵].</t>
+  </si>
+  <si>
+    <t>Entropy Bonus</t>
+  </si>
+  <si>
+    <t>بونوس انتروپی</t>
+  </si>
+  <si>
+    <t>جمله‌ای در تابع زیان که مدل را تشویق به کاوش و جلوگیری از همگرایی زودهنگام می‌کند [۱۰۱].</t>
+  </si>
+  <si>
+    <t>Surrogate Objective</t>
+  </si>
+  <si>
+    <t>تابع هدف جایگزین</t>
+  </si>
+  <si>
+    <t>تابعی که به عنوان تخمین‌گر کارایی سیاست عمل کرده و بهینه‌سازی روی آن انجام می‌شود [۸۶، ۹۱].</t>
+  </si>
+  <si>
+    <t>Pessimistic Bound</t>
+  </si>
+  <si>
+    <t>حد پایین بدبینانه</t>
+  </si>
+  <si>
+    <t>رویکردی در PPO که کمترین مقدار سود احتمالی را برای تضمین امنیت به‌روزرسانی در نظر می‌گیرد [۸۸، ۹۳].</t>
+  </si>
+  <si>
+    <t>Iteration</t>
+  </si>
+  <si>
+    <t>تکرار / حلقه اصلی</t>
+  </si>
+  <si>
+    <t>هر چرخه کامل از جمع‌آوری داده تا به‌روزرسانی سیاست در الگوریتم [۱۰۴].</t>
+  </si>
+  <si>
+    <t>Timesteps (T)</t>
+  </si>
+  <si>
+    <t>گام‌های زمانی</t>
+  </si>
+  <si>
+    <t>کوچکترین واحد زمانی پایش که در آن یک وضعیت مشاهده و یک کنش انجام می‌شود [۱۰۳].</t>
+  </si>
+  <si>
+    <t>Advantage Estimate (A^)</t>
+  </si>
+  <si>
+    <t>تخمین مزیت</t>
+  </si>
+  <si>
+    <t>معیاری که نشان می‌دهد یک کنش چقدر از میانگین کنش‌های دیگر بهتر بوده است [۹۰، ۱۰۳].</t>
+  </si>
+  <si>
+    <t>Discount Factor (γ)</t>
+  </si>
+  <si>
+    <t>ضریب تنزیل</t>
+  </si>
+  <si>
+    <t>وزنی که برای اهمیت پاداش‌های آینده نسبت به پاداش فعلی در نظر گرفته می‌شود [۱۲۰].</t>
+  </si>
+  <si>
+    <t>GAE Parameter (λ)</t>
+  </si>
+  <si>
+    <t>پارامتر GAE</t>
+  </si>
+  <si>
+    <t>ضریبی برای کنترل واریانس و سوگیری در تخمین تابع مزیت [۱۰۳، ۱۲۰].</t>
+  </si>
+  <si>
+    <t>Adam Stepsize</t>
+  </si>
+  <si>
+    <t>نرخ یادگیری Adam</t>
+  </si>
+  <si>
+    <t>سرعتی که بهینه‌ساز با آن پارامترهای شبکه عصبی را تغییر می‌دهد [۱۲۰].</t>
+  </si>
+  <si>
+    <t>Monotonic Improvement</t>
+  </si>
+  <si>
+    <t>بهبود یکنواخت</t>
+  </si>
+  <si>
+    <t>اصلی‌ترین ویژگی PPO و TRPO که تضمین می‌کند سیاست در هر گام بدتر نمی‌شود [۹۳، ۱۱۵].</t>
+  </si>
+  <si>
+    <t>Robustness</t>
+  </si>
+  <si>
+    <t>پایداری / تاب‌آوری</t>
+  </si>
+  <si>
+    <t>توانایی الگوریتم در عملکرد صحیح بدون نیاز به تنظیم دقیق (Fine-tuning) مداوم ابرپارامترها [۸۷].</t>
+  </si>
+  <si>
+    <t>Trade-off</t>
+  </si>
+  <si>
+    <t>موازنه / تعادل</t>
+  </si>
+  <si>
+    <t>ایجاد توازن بین دو عامل متضاد؛ مثلاً دقت امبدینگ در مقابل سرعت محاسبات در GraphSAGE [۳۴، ۳۹].</t>
+  </si>
+  <si>
+    <t>Generalization</t>
+  </si>
+  <si>
+    <t>تعمیم‌پذیری</t>
+  </si>
+  <si>
+    <t>توانایی مدل در پاسخگویی به گره‌ها یا گراف‌هایی که در زمان آموزش هرگز ندیده است [۱، ۳].</t>
+  </si>
+  <si>
+    <t>Incentive</t>
+  </si>
+  <si>
+    <t>انگیزه / محرک</t>
+  </si>
+  <si>
+    <t>در PPO، Clipping انگیزه‌ی عامل برای تغییرات افراطی و خروج از بازه امن را از بین می‌برد [۹۴، ۹۵].</t>
+  </si>
+  <si>
+    <t>Heuristically</t>
+  </si>
+  <si>
+    <t>به صورت ابتکاری</t>
+  </si>
+  <si>
+    <t>انتخاب پارامترها بر اساس تجربه و آزمایش، نه صرفاً بر پایه اثبات دقیق ریاضی [۹۹].</t>
+  </si>
+  <si>
+    <t>Empirically</t>
+  </si>
+  <si>
+    <t>به صورت تجربی</t>
+  </si>
+  <si>
+    <t>نتایجی که از طریق آزمایش و مشاهده به دست می‌آیند (در مقابل نتایج تئوریک محض) [۸۶، ۹۱].</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr defaultColWidth="32.42578125" defaultRowHeight="22.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" style="9" bestFit="1" customWidth="1"/>
@@ -3131,6 +3296,209 @@
       </c>
       <c r="C142" s="13" t="s">
         <v>371</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="14" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="C144" s="13" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A145" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="C145" s="13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A146" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A147" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="B147" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C147" s="13" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A148" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="C149" s="13" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A150" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C150" s="13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A151" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="B151" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C151" s="13" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A152" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C152" s="13" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="C153" s="13" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="C154" s="13" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A155" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="B155" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C155" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A156" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="C156" s="13" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A157" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="13" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A158" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B158" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="C158" s="13" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A159" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="B159" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="C159" s="13" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A160" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="C160" s="13" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A161" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="C161" s="13" t="s">
+        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/notes/Cumulative Vocabulary Table.xlsx
+++ b/notes/Cumulative Vocabulary Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Lessons ✒📝\Master\Term 3\Master's Theses\Paper\Paper_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B5218A-E8C2-4153-896C-22D3DD2A9E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C3F1AD-9F9D-4E39-9AF8-552C183E40E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="1080" windowWidth="17475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1095" yWindow="1425" windowWidth="17475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="479">
   <si>
     <t>کلمه تخصصی (English)</t>
   </si>
@@ -1309,6 +1309,162 @@
   </si>
   <si>
     <t>نتایجی که از طریق آزمایش و مشاهده به دست می‌آیند (در مقابل نتایج تئوریک محض) [۸۶، ۹۱].</t>
+  </si>
+  <si>
+    <t>Fail to Generalize</t>
+  </si>
+  <si>
+    <t>شکست در تعمیم‌پذیری</t>
+  </si>
+  <si>
+    <t>ناتوانی مدل در پاسخگویی به شرایط و توپولوژی‌های جدید و دیده‌نشده [۱، ۶].</t>
+  </si>
+  <si>
+    <t>Production Networks</t>
+  </si>
+  <si>
+    <t>شبکه‌های عملیاتی</t>
+  </si>
+  <si>
+    <t>محیط‌های واقعی و زنده شبکه (مانند همراه اول) که با داده‌های آزمایشگاهی متفاوتند [۱، ۷].</t>
+  </si>
+  <si>
+    <t>Iterative Algorithm</t>
+  </si>
+  <si>
+    <t>الگوریتم تکرارشونده</t>
+  </si>
+  <si>
+    <t>فرآیند مرحله‌به‌مرحله‌ای که برای به‌روزرسانی وضعیت گره‌ها در GNN اجرا می‌شود [۱۴، ۱۵].</t>
+  </si>
+  <si>
+    <t>Propagate</t>
+  </si>
+  <si>
+    <t>انتشار دادن</t>
+  </si>
+  <si>
+    <t>فرآیند پخش کردن اطلاعات ترافیکی و ساختاری در سراسر گراف شبکه [۱۵].</t>
+  </si>
+  <si>
+    <t>Hidden State (hk​)</t>
+  </si>
+  <si>
+    <t>وضعیت پنهان</t>
+  </si>
+  <si>
+    <t>بردار ویژگی غنی‌شده‌ای که تمام دانش محلی و همسایگی یک گره را در خود ذخیره می‌کند [۱۵، ۱۶].</t>
+  </si>
+  <si>
+    <t>MDP (Markov Decision Process)</t>
+  </si>
+  <si>
+    <t>فرآیند تصمیم‌گیری مارکوف</t>
+  </si>
+  <si>
+    <t>چارچوب ریاضی برای مدل‌سازی تصمیم‌گیری در شرایطی که نتایج بخشی تصادفی و بخشی تحت کنترل هستند [۲۴].</t>
+  </si>
+  <si>
+    <t>Infeasible</t>
+  </si>
+  <si>
+    <t>غیرقابل‌اجرا / نشدنی</t>
+  </si>
+  <si>
+    <t>وضعیتی که در آن به دلیل پیچیدگی بالا، حل مسئله با منابع موجود ممکن نیست [۲۴].</t>
+  </si>
+  <si>
+    <t>Link Betweenness</t>
+  </si>
+  <si>
+    <t>بینابینی لینک</t>
+  </si>
+  <si>
+    <t>شاخصی که نشان می‌دهد یک لینک چقدر در مسیرهای کوتاه شبکه نقش مرکزی دارد [۲۷].</t>
+  </si>
+  <si>
+    <t>Converge Faster</t>
+  </si>
+  <si>
+    <t>همگرایی سریع‌تر</t>
+  </si>
+  <si>
+    <t>رسیدن مدل هوش مصنوعی به پاسخ بهینه در زمان کوتاه‌تر و با خطای کمتر [۲۷].</t>
+  </si>
+  <si>
+    <t>ویژگی‌ای که باعث می‌شود خروجی مدل با تغییر ترتیب (نام) گره‌ها تغییر نکند [۲۸].</t>
+  </si>
+  <si>
+    <t>Candidate Paths</t>
+  </si>
+  <si>
+    <t>مسیرهای کاندید</t>
+  </si>
+  <si>
+    <t>مجموعه‌ای از مسیرهای منتخب (معمولاً کوتاهترین‌ها) که عامل DRL بین آن‌ها حق انتخاب دارد [۲۹، ۳۵].</t>
+  </si>
+  <si>
+    <t>برداری که دانش ساختاری و ترافیکی لینک را در خود فشرده کرده است [۱۵، ۱۶].</t>
+  </si>
+  <si>
+    <t>Readout Function</t>
+  </si>
+  <si>
+    <t>تابع بازخوانی</t>
+  </si>
+  <si>
+    <t>لایه نهایی که اطلاعات کل گراف را برای تخمین سودمندی یک کنش (Q-value) جمع‌بندی می‌کند [۱۶، ۳۳].</t>
+  </si>
+  <si>
+    <t>One-hot Encoding</t>
+  </si>
+  <si>
+    <t>کدگذاری تک‌یک</t>
+  </si>
+  <si>
+    <t>روشی برای نمایش کنش‌های گسسته (مانند انتخاب یک مسیر خاص) در فضای برداری GNN [۲۹].</t>
+  </si>
+  <si>
+    <t>Stochastic Gradient Descent</t>
+  </si>
+  <si>
+    <t>گرادیان کاهشی تصادفی</t>
+  </si>
+  <si>
+    <t>الگوریتم بهینه‌سازی که برای آموزش پارامترهای GNN در این مقاله استفاده شده است [۴۰].</t>
+  </si>
+  <si>
+    <t>Message-passing Steps (T)</t>
+  </si>
+  <si>
+    <t>گام‌های پیام‌رسانی</t>
+  </si>
+  <si>
+    <t>تعداد دفعاتی که اطلاعات بین لینک‌ها مبادله می‌شود (در این مقاله T=7) [۳۳، ۴۰].</t>
+  </si>
+  <si>
+    <t>Readout Function (R)</t>
+  </si>
+  <si>
+    <t>لایه‌ای که وضعیت کل گراف را برای تصمیم‌گیری نهایی خلاصه می‌کند [۱۶، ۳۳].</t>
+  </si>
+  <si>
+    <t>Inference Time</t>
+  </si>
+  <si>
+    <t>زمان استنتاج</t>
+  </si>
+  <si>
+    <t>زمانی که طول می‌کشد تا مدل برای یک ترافیک جدید، مسیر بهینه را پیدا کند (در حدود چند میلی‌ثانیه) [۱۲، ۶۰، ۶۱].</t>
+  </si>
+  <si>
+    <t>Link Entity</t>
+  </si>
+  <si>
+    <t>موجودیت لینک</t>
+  </si>
+  <si>
+    <t>در این معماری به جای گره‌ها، لینک‌ها به عنوان بازیگران اصلی گراف در نظر گرفته شده‌اند [۳۲].</t>
   </si>
 </sst>
 </file>
@@ -1749,7 +1905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D181"/>
   <sheetFormatPr defaultColWidth="32.42578125" defaultRowHeight="22.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" style="9" bestFit="1" customWidth="1"/>
@@ -3499,6 +3655,218 @@
       </c>
       <c r="C161" s="13" t="s">
         <v>426</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="14"/>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="B163" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="C163" s="13" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A164" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="B164" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="C164" s="13" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A165" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="B165" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="C165" s="13" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C166" s="13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A167" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="C167" s="13" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A168" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="B168" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="C168" s="13" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A169" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="C169" s="13" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A170" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="C170" s="13" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="C171" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A172" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C172" s="13" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A173" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="C173" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A174" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="C174" s="13" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A175" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="C175" s="13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A176" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="C176" s="13" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A177" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="C177" s="13" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A178" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C178" s="13" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="B179" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="C179" s="13" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A180" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B180" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="C180" s="13" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A181" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="C181" s="13" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -3516,6 +3884,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>